--- a/resources/residence/residence_building.xlsx
+++ b/resources/residence/residence_building.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-1095" windowWidth="29040" windowHeight="15720" tabRatio="708" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidenceBuilding" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuildingType" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuildingCamera" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AttributeText" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuildingInteract" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ResidenceBuilding" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BuildingType" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BuildingCamera" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="AttributeText" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="BuildingInteract" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">ResidenceBuilding!#REF!</definedName>
@@ -7539,7 +7539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="20.75" customWidth="1" style="8" min="1" max="1"/>
@@ -8538,6 +8538,33 @@
       <c r="Q16" s="0" t="n"/>
       <c r="R16" s="0" t="n"/>
       <c r="S16" s="0" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>灵泉</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="0" t="n"/>
+      <c r="G17" s="0" t="n"/>
+      <c r="H17" s="0" t="n"/>
+      <c r="I17" s="0" t="n"/>
+      <c r="J17" s="0" t="n"/>
+      <c r="K17" s="0" t="n"/>
+      <c r="L17" s="0" t="n"/>
+      <c r="M17" s="0" t="n"/>
+      <c r="N17" s="0" t="n"/>
+      <c r="O17" s="0" t="n"/>
+      <c r="P17" s="0" t="n"/>
+      <c r="Q17" s="0" t="n"/>
+      <c r="R17" s="0" t="n"/>
+      <c r="S17" s="0" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:S2">
